--- a/public/downloads/三省份容量补偿对照表.xlsx
+++ b/public/downloads/三省份容量补偿对照表.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0&quot;h&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -165,13 +164,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -552,11 +551,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -566,10 +564,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基于114号文容量电价公式：年补偿收入 = 煤电容量电价 × (放电时长 ÷ 高峰时长) × 装机容量</t>
+          <t>基于114号文容量电价公式：年补偿收入 = 煤电容量电价 x (放电时长 / 高峰时长) x 装机容量</t>
         </is>
       </c>
     </row>
@@ -606,12 +604,6 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -633,11 +625,6 @@
       <c r="E7" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>各省发改委文件</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -659,62 +646,47 @@
       <c r="E8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>陕西已定6h，甘浙暂按6h</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>装机容量</t>
+          <t>储能放电时长</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>小时</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>统一假设</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>储能放电时长</t>
+          <t>装机容量</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>小时</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>可按实际修改</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -750,11 +722,6 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -779,10 +746,6 @@
         <f>MIN(E9/E8,1)</f>
         <v/>
       </c>
-      <c r="F15" s="6">
-        <f>MIN(储能时长/高峰时长,1)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -807,10 +770,6 @@
         <f>E7*E15</f>
         <v/>
       </c>
-      <c r="F16" s="6">
-        <f>煤电容量电价×折算比例</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -824,19 +783,15 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>C16*C9*1000/10000</f>
+        <f>C16*C10*1000/10000</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>D16*D9*1000/10000</f>
+        <f>D16*D10*1000/10000</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>E16*E9*1000/10000</f>
-        <v/>
-      </c>
-      <c r="F17" s="9">
-        <f>补偿标准×装机MW×1000÷10000</f>
+        <f>E16*E10*1000/10000</f>
         <v/>
       </c>
     </row>
@@ -863,10 +818,6 @@
         <f>E17*20</f>
         <v/>
       </c>
-      <c r="F18" s="6">
-        <f>年收入×20年</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -879,7 +830,7 @@
           <t>万元/年</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="8">
@@ -890,10 +841,6 @@
         <f>E17-C17</f>
         <v/>
       </c>
-      <c r="F19" s="6">
-        <f>本省收入-陕西收入</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -923,22 +870,21 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="13">
-        <f>MIN(C8/C8,1)*C7*1000/10000</f>
+        <f>MIN(2/C8,1)*C7*C10*1000/10000</f>
         <v/>
       </c>
       <c r="C24" s="13">
-        <f>MIN(D8/D8,1)*D7*1000/10000</f>
+        <f>MIN(2/D8,1)*D7*D10*1000/10000</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>MIN(E8/E8,1)*E7*1000/10000</f>
+        <f>MIN(2/E8,1)*E7*E10*1000/10000</f>
         <v/>
       </c>
     </row>
@@ -947,15 +893,15 @@
         <v>4</v>
       </c>
       <c r="B25" s="15">
-        <f>MIN(C9/C8,1)*C7*1000/10000</f>
+        <f>MIN(4/C8,1)*C7*C10*1000/10000</f>
         <v/>
       </c>
       <c r="C25" s="15">
-        <f>MIN(D9/D8,1)*D7*1000/10000</f>
+        <f>MIN(4/D8,1)*D7*D10*1000/10000</f>
         <v/>
       </c>
       <c r="D25" s="15">
-        <f>MIN(E9/E8,1)*E7*1000/10000</f>
+        <f>MIN(4/E8,1)*E7*E10*1000/10000</f>
         <v/>
       </c>
     </row>
@@ -964,15 +910,15 @@
         <v>6</v>
       </c>
       <c r="B26" s="13">
-        <f>MIN(C10/C8,1)*C7*1000/10000</f>
+        <f>MIN(6/C8,1)*C7*C10*1000/10000</f>
         <v/>
       </c>
       <c r="C26" s="13">
-        <f>MIN(D10/D8,1)*D7*1000/10000</f>
+        <f>MIN(6/D8,1)*D7*D10*1000/10000</f>
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>MIN(E10/E8,1)*E7*1000/10000</f>
+        <f>MIN(6/E8,1)*E7*E10*1000/10000</f>
         <v/>
       </c>
     </row>
@@ -981,15 +927,15 @@
         <v>8</v>
       </c>
       <c r="B27" s="15">
-        <f>MIN(C11/C8,1)*C7*1000/10000</f>
+        <f>MIN(8/C8,1)*C7*C10*1000/10000</f>
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>MIN(D11/D8,1)*D7*1000/10000</f>
+        <f>MIN(8/D8,1)*D7*D10*1000/10000</f>
         <v/>
       </c>
       <c r="D27" s="15">
-        <f>MIN(E11/E8,1)*E7*1000/10000</f>
+        <f>MIN(8/E8,1)*E7*E10*1000/10000</f>
         <v/>
       </c>
     </row>
@@ -1001,13 +947,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A29:E29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1020,16 +963,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1039,40 +980,37 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>以下结果为纯文本说明，具体计算请参考「参数输入与对比」表</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>计算项</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>陕西公式</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>陕西结果</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>甘肃公式</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>甘肃结果</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>浙江公式</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>浙江结果</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
@@ -1083,24 +1021,22 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>MIN(4/6,1)</f>
+        <f>MIN(4/6,1)=66.7%</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>MIN(4/6,1)</f>
+        <f>MIN(4/6,1)=66.7%</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>MIN(4/6,1)</f>
+        <f>MIN(4/6,1)=66.7%</f>
         <v/>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>储能定价核心参数</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
+          <t>储能时长÷高峰时长，最高为1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -1108,25 +1044,26 @@
           <t>(2) 补偿标准</t>
         </is>
       </c>
-      <c r="B6" s="18">
-        <f>165×折算比例</f>
-        <v/>
-      </c>
-      <c r="C6" s="18">
-        <f>330×折算比例</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
-        <f>200×折算比例</f>
-        <v/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>165×66.7%=110元/kW·年</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>330×66.7%=220元/kW·年</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>200×66.7%=133元/kW·年</t>
+        </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>按比例折算</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
+          <t>煤电电价×折算比例（浙江直补200，不折算）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
@@ -1134,25 +1071,26 @@
           <t>(3) 年补偿收入</t>
         </is>
       </c>
-      <c r="B7" s="18">
-        <f>标准×100MW</f>
-        <v/>
-      </c>
-      <c r="C7" s="18">
-        <f>标准×100MW</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
-        <f>标准×100MW</f>
-        <v/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>110×100MW=1,100万元</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>220×100MW=2,200万元</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>133×100MW=1,330万元（直补200→2,000万元）</t>
+        </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>直接按装机计算</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
+          <t>标准×装机容量</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -1160,28 +1098,30 @@
           <t>(4) 月补偿收入</t>
         </is>
       </c>
-      <c r="B8" s="18">
-        <f>年收入÷12</f>
-        <v/>
-      </c>
-      <c r="C8" s="18">
-        <f>年收入÷12</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
-        <f>年收入÷12</f>
-        <v/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>1,100÷12=92万元/月</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>2,200÷12=183万元/月</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>2,000÷12=167万元/月</t>
+        </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>按月结算现金流</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
+          <t>年收入÷12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
